--- a/CPRG-305-B/group-assignment-2/DealerOps_Group_Assignment_2_Test_Cases.xlsx
+++ b/CPRG-305-B/group-assignment-2/DealerOps_Group_Assignment_2_Test_Cases.xlsx
@@ -787,7 +787,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Jackson Warga</t>
+          <t>Xiaomei He</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Logan Jones</t>
+          <t>Daniel Watson</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
@@ -920,7 +920,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Logan Jones</t>
+          <t>Daniel Watson</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
@@ -981,7 +981,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Logan Jones</t>
+          <t>Daniel Watson</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Logan Jones</t>
+          <t>Daniel Watson</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Logan Jones</t>
+          <t>Daniel Watson</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Logan Jones</t>
+          <t>Daniel Watson</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Logan Jones</t>
+          <t>Daniel Watson</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Logan Jones</t>
+          <t>Daniel Watson</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Jackson Warga</t>
+          <t>Xiaomei He</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>Jackson Warga</t>
+          <t>Xiaomei He</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Jackson Warga</t>
+          <t>Xiaomei He</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Logan Jones</t>
+          <t>Daniel Watson</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Logan Jones</t>
+          <t>Daniel Watson</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Logan Jones</t>
+          <t>Daniel Watson</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Logan Jones</t>
+          <t>Daniel Watson</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>Logan Jones</t>
+          <t>Daniel Watson</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr"/>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>Logan Jones</t>
+          <t>Daniel Watson</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr"/>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>Logan Jones</t>
+          <t>Daniel Watson</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr"/>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>Logan Jones</t>
+          <t>Daniel Watson</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>Logan Jones</t>
+          <t>Daniel Watson</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Logan Jones</t>
+          <t>Daniel Watson</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>Logan Jones</t>
+          <t>Daniel Watson</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Logan Jones</t>
+          <t>Daniel Watson</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>Logan Jones</t>
+          <t>Daniel Watson</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>Jackson Warga</t>
+          <t>Xiaomei He</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>Jackson Warga</t>
+          <t>Xiaomei He</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>Jackson Warga</t>
+          <t>Xiaomei He</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>Logan Jones</t>
+          <t>Daniel Watson</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>Logan Jones</t>
+          <t>Daniel Watson</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>Logan Jones</t>
+          <t>Daniel Watson</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>Logan Jones</t>
+          <t>Daniel Watson</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>Bedgel Fadhil Ndam Woukouo</t>
+          <t>Daniel Watson</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>Bedgel Fadhil Ndam Woukouo</t>
+          <t>Daniel Watson</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>Bedgel Fadhil Ndam Woukouo</t>
+          <t>Daniel Watson</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>Bedgel Fadhil Ndam Woukouo</t>
+          <t>Daniel Watson</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>Logan Jones</t>
+          <t>Daniel Watson</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>Bedgel Fadhil Ndam Woukouo</t>
+          <t>Daniel Watson</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>Bedgel Fadhil Ndam Woukouo</t>
+          <t>Daniel Watson</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr"/>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>Bedgel Fadhil Ndam Woukouo</t>
+          <t>Daniel Watson</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr"/>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>Bedgel Fadhil Ndam Woukouo</t>
+          <t>Daniel Watson</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr"/>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>Bedgel Fadhil Ndam Woukouo</t>
+          <t>Daniel Watson</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>Bedgel Fadhil Ndam Woukouo</t>
+          <t>Daniel Watson</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr"/>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>Bedgel Fadhil Ndam Woukouo</t>
+          <t>Daniel Watson</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr"/>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>Bedgel Fadhil Ndam Woukouo</t>
+          <t>Daniel Watson</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr"/>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>Bedgel Fadhil Ndam Woukouo</t>
+          <t>Daniel Watson</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr"/>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>Bedgel Fadhil Ndam Woukouo</t>
+          <t>Daniel Watson</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr"/>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>Bedgel Fadhil Ndam Woukouo</t>
+          <t>Daniel Watson</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr"/>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>Bedgel Fadhil Ndam Woukouo</t>
+          <t>Daniel Watson</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr"/>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>Bedgel Fadhil Ndam Woukouo</t>
+          <t>Daniel Watson</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr"/>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>Bedgel Fadhil Ndam Woukouo</t>
+          <t>Daniel Watson</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr"/>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Yuandong Yang (Robin), Bedgel Fadhil Ndam Woukouo, Jackson Warga, Logan Jones</t>
+          <t>Yuandong Yang, Daniel Watson, Xiaomei He</t>
         </is>
       </c>
     </row>

--- a/CPRG-305-B/group-assignment-2/DealerOps_Group_Assignment_2_Test_Cases.xlsx
+++ b/CPRG-305-B/group-assignment-2/DealerOps_Group_Assignment_2_Test_Cases.xlsx
@@ -10,7 +10,9 @@
     <sheet name="Test Cases" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Cases'!$A$1:$N$71</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -18,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,12 +31,15 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="001F4E78"/>
       <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -76,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -85,6 +90,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -451,26 +457,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N56"/>
+  <dimension ref="A1:N71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="38" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Test Case ID</t>
@@ -513,3445 +519,4688 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Environment</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Tested By</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Test Date</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Comments</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ST-01</t>
+          <t>RV-01</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>REQ-AUTH</t>
+          <t>AUTH-07, AUTH-09</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Review authentication and JWT configuration in dealer-core and dealer-gateway</t>
+          <t>Review how the dealership is resolved and how cross-dealership ids are answered</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Source for dealer-core SecurityConfig and gateway JwtAuthenticationFilter is available</t>
+          <t>Working tree available; TenantGuard, MembershipService and the business controllers open</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>1. Open dealer-core SecurityConfig and JwtTokenProvider
-2. Open dealer-gateway JwtAuthenticationFilter
-3. Verify shared JWT secret source and expiry policy
-4. Verify all protected routes require authentication</t>
+          <t>1. Trace the dealership from the JWT sub (username) to the active membership row in TenantGuard
+2. Grep the controllers and DTOs for any read of a client-supplied dealerId
+3. Confirm every repository query filters on the resolved dealer id
+4. Confirm a resource of another dealership answers 404, not 403</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>No unprotected business route; JWT secret sourced from environment; expiry enforced consistently</t>
+          <t>The dealership comes only from the signed-in identity, client dealerId is ignored, and another dealership's id is indistinguishable from a missing one (404 NOT_FOUND)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Dev (static review)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Dev - static review of the working tree (no runtime)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
           <t>Yuandong Yang</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>Static review — chapter 5 traceability</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Phase: requirements and design review; traces BE-01, BE-16</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>ST-02</t>
+          <t>RV-02</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>REQ-TENANT</t>
+          <t>AD-07, AD-09, AD-11, AD-12</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Review dealer membership and tenant isolation enforcement</t>
+          <t>Review the five ad-check states and the ready/export gate</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>DealerMembership entity, service, and controller source available</t>
+          <t>CheckStatusMapper, ComplianceCheckService, OmvicRuleEngine and the listing controller open</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>1. Trace dealerId resolution from JWT claim through service layer
-2. Confirm no controller trusts request-body dealerId
-3. Confirm repository queries filter by authenticated dealerId</t>
+          <t>1. List the states the mapper can return (NOT_CHECKED, BLOCKED, NEEDS_AI, PASSED, STALE)
+2. Confirm a hard rule hit returns BLOCKED without calling /internal/v1/ad-check
+3. Confirm a passed check of older content maps to STALE and a non-passed one to NEEDS_AI
+4. Confirm ready and export require PASSED on the current content version</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>All data access scoped by authenticated membership; client-supplied dealerId is ignored or rejected</t>
+          <t>Each state has one code path, AI is skipped on a hard miss, and ready/export are reachable only from PASSED on the current version</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Dev (static review)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Yuandong Yang</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr"/>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Dev - static review of the working tree (no runtime)</t>
+        </is>
+      </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Static review — tenant boundary</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+          <t>Xiaomei He</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Phase: requirements and design review; traces BE-07, BE-09, BE-10</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ST-03</t>
+          <t>RV-03</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>REQ-INV</t>
+          <t>SEC-02, SEC-05, SHOP-05</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Review inventory lifecycle state machine (DRAFT→READY→SOLD) and sold-lock guard</t>
+          <t>Review the gateway route table, CORS, internal-token guard and rate limits</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>VehicleService, VehicleStatus enum, and listing controller source available</t>
+          <t>DealerOps.Gateway appsettings and InternalCallerGuard open</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1. Walk through status transitions in VehicleService
-2. Confirm sold vehicles reject mutating endpoints
-3. Confirm stale-readiness invalidation when vehicle details change</t>
+          <t>1. Inventory every route the gateway exposes under /api/v1/**
+2. Confirm /api/v1/public/** passes without a token and everything else needs a valid JWT
+3. Confirm core and ai-service answer only with X-Dealer-Internal and the gateway never forwards it from a client
+4. Record the configured CORS origins and the per-IP inquiry limit</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Transitions are explicit; SOLD vehicles rejected on edit; stale readiness recomputed</t>
+          <t>Only intended business routes are public, the internal token is server-side only, CORS is limited to the configured web origins, and the inquiry limit is configurable</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Dev (static review)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Yuandong Yang</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr"/>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Dev - static review of the working tree (no runtime)</t>
+        </is>
+      </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Static review — inventory</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+          <t>Daniel Watson</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Phase: requirements and design review; traces BE-14</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>ST-04</t>
+          <t>RV-04</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>REQ-AI</t>
+          <t>AUD-03, AUD-04, AUD-16, AUD-17</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Review ai-service internal-only enforcement and prompt boundaries</t>
+          <t>Review the audit record shape, stored values and who may read them</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>ai-service source, InternalHeaderFilter, and prompt builder available</t>
+          <t>AuditService, the audit controllers and the logging project open</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1. Verify X-Dealer-Internal header is required on all AI endpoints
-2. Review prompt builder to confirm no secrets or PII templated
-3. Review timeout and retry configuration</t>
+          <t>1. Confirm each row stores actor, action, entity, timestamp, client IP and the replaced values
+2. Confirm customer contact values are recorded in the audit trail but scrubbed from application logs and AI prompts
+3. Confirm record history, the dealership log and the platform log are manager-only and admin-only
+4. Confirm an unknown entity type or action is rejected rather than written</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>AI endpoints reject external calls; prompts contain only structured facts; timeouts bounded</t>
+          <t>Audit rows are complete and append-only, contact data never reaches logs or prompts, and staff have no audit access</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Dev (static review)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Dev - static review of the working tree (no runtime)</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
           <t>Xiaomei He</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>Static review — AI boundary</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Phase: requirements and design review; traces BE-11, EXT-17</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>ST-05</t>
+          <t>RV-05</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>REQ-GW</t>
+          <t>DMS-11, DMS-12, PAY-02, PAY-05</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Review gateway route table, CORS, and timeout configuration</t>
+          <t>Review the sold-vehicle lock and the payment ledger invariants</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>dealer-gateway application.yml and route configuration available</t>
+          <t>VehicleService, VehiclePaymentService and the sell endpoint open</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1. Inventory all public routes exposed via 8080
-2. Verify no direct route to ai-service 8082 is published
-3. Verify CORS allowed origins restrict to configured frontend
-4. Verify per-route timeout and circuit breaker</t>
+          <t>1. List the purchase fields locked after a sale and the endpoints that enforce the lock
+2. Confirm a second sale is refused
+3. Confirm the paid total cannot exceed the sold price and paidOn sits between the sold date and today
+4. Confirm the ledger read and the payment delete are manager-only</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Only intended business routes exposed; AI port not reachable from browser; CORS restrictive; timeouts set</t>
+          <t>Every locked field is covered by one guard returning 409 SOLD_LOCKED, a second sale is refused, and the ledger rules and role split are implemented as specified</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Dev (static review)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Dev - static review of the working tree (no runtime)</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
           <t>Daniel Watson</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>Static review — gateway</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Phase: requirements and design review; traces BE-03, EXT-12, EXT-19</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>UT-01</t>
+          <t>RV-06</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>REQ-AUTH</t>
+          <t>All Must requirements</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Password hashing uses BCrypt with configured strength</t>
+          <t>Audit requirement coverage of this workbook before execution starts</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>dealer-core unit test environment</t>
+          <t>requirements/DealerOps-Requirements.md and this workbook available</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1. Call PasswordEncoder.encode("P@ssw0rd!")
-2. Verify output starts with $2a$ or $2b$
-3. Verify encoder.matches raw/encoded</t>
+          <t>1. List every Must requirement id in the requirements specification
+2. Map each id to at least one case in this workbook
+3. Record ids with no case and raise them as planning defects
+4. Have the three members approve the mapping</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Hash is BCrypt and raw password matches; different calls yield different hashes</t>
+          <t>Every Must requirement has at least one case and one owner; gaps are logged before execution, not discovered during it</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Dev (unit, JUnit)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Daniel Watson</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>Dev - static review of the working tree (no runtime)</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Yuandong Yang</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Phase: requirements and design review; entry gate for all later phases</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>UT-02</t>
+          <t>UT-01</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>REQ-AUTH</t>
+          <t>DMS-04</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>JwtTokenProvider rejects expired tokens</t>
+          <t>VIN normalisation accepts 17 valid characters and rejects I, O, Q and wrong lengths</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>JwtTokenProvider bean available with test secret</t>
+          <t>DealerOps.Core builds; no database needed</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1. Generate token with expiry = now-1s
-2. Call validateToken(token)</t>
+          <t>1. Pass '1hgcm82633a004352' and assert it is stored upper-cased
+2. Pass a 16-character VIN
+3. Pass a VIN containing I, O and Q in turn
+4. Pass 17 valid characters</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>validateToken returns false / throws expired token exception</t>
+          <t>Lower case is upper-cased; 16 characters and any I/O/Q are rejected with the field error 'VIN must be 17 letters or digits, without I, O or Q.'; a valid VIN is accepted</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Dev (unit, JUnit)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Dev - xUnit on DealerOps.Core (.NET 10 SDK, no database)</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
           <t>Daniel Watson</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Phase: unit; boundary-value analysis</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>UT-03</t>
+          <t>UT-02</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>REQ-TENANT</t>
+          <t>DMS-01</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>DealerContext resolver returns dealerId from authenticated principal only</t>
+          <t>Money validation accepts two decimals and rejects more decimals and negative values</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>DealerContext resolver with mocked security context</t>
+          <t>DealerOps.Core builds</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1. Set SecurityContext with principal containing dealerId=A
-2. Call resolve()
-3. Repeat with no principal</t>
+          <t>1. Validate purchase cost 18900.00 and 18900.5
+2. Validate 18900.555
+3. Validate -1
+4. Validate 0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Returns 'A' with principal; throws Unauthorized when principal is absent; ignores request-provided dealerId</t>
+          <t>Two decimals and zero are accepted; three decimals and a negative amount are rejected with 400 VALIDATION naming the field</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Dev (unit, JUnit)</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Dev - xUnit on DealerOps.Core (.NET 10 SDK, no database)</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
           <t>Daniel Watson</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Phase: unit; equivalence partitioning</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>UT-04</t>
+          <t>UT-03</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>REQ-INV</t>
+          <t>DMS-10</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Vehicle validator rejects invalid VIN length</t>
+          <t>Selling a vehicle requires the sold date and sold price together</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>VehicleValidator unit scope</t>
+          <t>DealerOps.Core builds</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1. Validate vehicle with VIN of 16 chars
-2. Validate vehicle with VIN of 17 valid chars</t>
+          <t>1. Call the sell validator with only soldOn
+2. With only soldPrice
+3. With both and price 0
+4. With both and a valid price</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16-char VIN rejected with VIN_INVALID; 17-char valid VIN accepted</t>
+          <t>Either value alone and a price of 0 are rejected (SOLD_PAIR_REQUIRED / VALIDATION); the valid pair is accepted</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Dev (unit, JUnit)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Dev - xUnit on DealerOps.Core (.NET 10 SDK, no database)</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>Daniel Watson</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>Boundary check</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Phase: unit; traces BE-15</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>UT-05</t>
+          <t>UT-04</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>REQ-INV</t>
+          <t>AD-03, AD-07</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>VehicleService.update rejects edits on SOLD vehicle</t>
+          <t>OmvicRuleEngine blocks a CASH ad with no advertised price</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>VehicleService with mocked repository returning SOLD vehicle</t>
+          <t>DealerOps.Core builds; rule engine fixtures available</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1. Call update(id, newPrice) on SOLD vehicle</t>
+          <t>1. Build a CASH listing whose body has the dealership name but no price
+2. Run the rule engine
+3. Inspect the hard findings</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Throws VehicleLockedException with status=SOLD</t>
+          <t>A hard finding PRICE_MISSING with severity BLOCK is returned and the recommendation is BLOCKED</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Dev (unit, JUnit)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Daniel Watson</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Dev - xUnit on DealerOps.Core (.NET 10 SDK, no database)</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Xiaomei He</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Phase: unit; fixture FX family, design/17</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>UT-06</t>
+          <t>UT-05</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>REQ-COMP</t>
+          <t>AD-04</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Compliance evaluator flags listing without current evidence as NOT_READY</t>
+          <t>A FINANCE ad without an APR is blocked and a cash price is still required</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>ComplianceEvaluator unit scope</t>
+          <t>DealerOps.Core builds</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1. Build listing with no compliance evidence
-2. Call evaluate(listing)</t>
+          <t>1. Run a FINANCE ad with a monthly payment but no APR
+2. Add an APR but no cash price
+3. Add both</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Result = NOT_READY with reason MISSING_COMPLIANCE</t>
+          <t>No APR gives hard FINANCE_APR_MISSING; a payment without a cash price gives hard FINANCE_CASH_PRICE_MISSING; with both the ad reaches the AI step</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Dev (unit, JUnit)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Daniel Watson</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Dev - xUnit on DealerOps.Core (.NET 10 SDK, no database)</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Xiaomei He</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Phase: unit; traces CL-4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>UT-07</t>
+          <t>UT-06</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>REQ-COMP</t>
+          <t>AD-04</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Compliance evidence invalidated when key vehicle fields change</t>
+          <t>Lease rules require the lease statement, APR and excess-kilometre cost</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Listing with PASSED evidence; evaluator unit scope</t>
+          <t>DealerOps.Core builds</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1. Mutate vehicle.year on the linked vehicle
-2. Re-evaluate listing readiness</t>
+          <t>1. Run a LEASE ad with no lease statement and no APR
+2. Add both but no excess-kilometre cost
+3. State an allowance in the copy that is lower than the checklist allowance</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Evaluator reports STALE_EVIDENCE and listing is not Ready/exportable</t>
+          <t>LEASE_STATEMENT_MISSING and LEASE_APR_MISSING block; LEASE_EXCESS_KM_MISSING blocks; the mismatch is judged on the lower allowance and raises LEASE_ALLOWANCE_MISMATCH as REVIEW</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Dev (unit, JUnit)</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Daniel Watson</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Dev - xUnit on DealerOps.Core (.NET 10 SDK, no database)</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>Xiaomei He</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Phase: unit; design/17 amendment 2026-10-20</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>UT-08</t>
+          <t>UT-07</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>REQ-AI</t>
+          <t>AD-11</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>AI client maps upstream 504 to AiTimeoutException</t>
+          <t>CheckStatusMapper turns an outdated passed check into STALE and an outdated other check into NEEDS_AI</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>AI WebClient configured with 2s timeout and mock server returning delay</t>
+          <t>DealerOps.Core builds</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1. Call AiClient.check(request) against delaying stub
-2. Assert exception type</t>
+          <t>1. Map a PASSED check whose content version is older than the listing
+2. Map a BLOCKED check of older content
+3. Map a PASSED check of the current version</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>AiTimeoutException raised; no partial result stored</t>
+          <t>Older passed -&gt; STALE; older blocked -&gt; NEEDS_AI; current passed -&gt; PASSED</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Dev (unit, JUnit)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Dev - xUnit on DealerOps.Core (.NET 10 SDK, no database)</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
           <t>Xiaomei He</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>Timeout mapping</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Phase: unit; traces BE-07</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>UT-09</t>
+          <t>UT-08</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>REQ-AI</t>
+          <t>AI-02, AD-09</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>AI prompt builder excludes customer PII fields</t>
+          <t>The AI client maps every provider failure to an unavailable result, never to a pass</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>PromptBuilder with sample listing including customer phone and email</t>
+          <t>DealerOps.Core and DealerOps.AiService build; provider client stubbed</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1. Build prompt for ad-check on listing with embedded customer contact
-2. Inspect generated prompt text</t>
+          <t>1. Make the stub exceed the 15 s timeout
+2. Return 500
+3. Return an empty body
+4. Remove the API key</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Prompt contains only vehicle facts; no customer email, phone, or secret present</t>
+          <t>The results are AI_TIMEOUT, AI_PROVIDER_FAILED, AI_PROVIDER_FAILED and AI_KEY_MISSING; none maps to PASSED and none throws an unhandled exception</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Dev (unit, JUnit)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>Dev - xUnit on DealerOps.Core (.NET 10 SDK, no database)</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
           <t>Xiaomei He</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>No-leak check</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Phase: unit; traces BE-08</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>UT-10</t>
+          <t>UT-09</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>REQ-AI</t>
+          <t>CRM-12, AI-04</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>AI client returns BLOCK verdict unchanged when provider output is BLOCK</t>
+          <t>Customer contact data never enters an AI prompt or an assistant answer</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Mock provider returning BLOCK verdict with reason</t>
+          <t>DealerOps.Core builds; prompt builder reachable from a test</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1. Call AiClient.check(request)
-2. Inspect returned verdict and reasons</t>
+          <t>1. Build an ad-check prompt for a listing whose vehicle is linked to a customer
+2. Build an assistant payload for a keyword that matches that customer
+3. Search both payloads for the phone, e-mail and home address</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Verdict = BLOCK; reasons preserved verbatim; no silent conversion to PASS</t>
+          <t>Neither payload contains a phone, e-mail or address; the assistant cards carry ids and public vehicle facts only</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Dev (unit, JUnit)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Dev - xUnit on DealerOps.Core (.NET 10 SDK, no database)</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>Xiaomei He</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Phase: unit; traces BE-12</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>IT-01</t>
+          <t>UT-10</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>REQ-AUTH</t>
+          <t>AUD-04, AUD-13</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>POST /api/auth/login with valid credentials returns 200 and JWT</t>
+          <t>An update writes the replaced values and the application log stays free of contact data</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Seed user admin@dealer-a.example with known password exists</t>
+          <t>DealerOps.Core builds</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1. POST /api/auth/login { username, password }</t>
+          <t>1. Update a customer phone and e-mail through the service
+2. Read the audit row that was produced
+3. Read the log lines produced by the same call</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200; response contains accessToken (JWT); claims include dealerId</t>
+          <t>The audit row holds both the previous and the new values; the log lines name the entity and action only, with no contact values</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Dev (integration, MockMvc + Testcontainers MySQL)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Daniel Watson</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Dev - xUnit on DealerOps.Core (.NET 10 SDK, no database)</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>Xiaomei He</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Phase: unit; traces BE-11, EXT-17</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>IT-02</t>
+          <t>UT-11</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>REQ-AUTH</t>
+          <t>PAY-01, PAY-02</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>POST /api/auth/login with wrong password returns 401</t>
+          <t>Payment validation keeps the ledger inside the sold price and the sale window</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Seed user exists</t>
+          <t>DealerOps.Core builds</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1. POST /api/auth/login with incorrect password</t>
+          <t>1. Record 25,000 against a vehicle sold for 21,000
+2. Record 6,000 and then 15,000
+3. Record a payment dated before the sold date
+4. Record a payment against an in-stock vehicle</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>HTTP 401; no token; response does not reveal whether username exists</t>
+          <t>Over the balance, a date outside the sale window and an in-stock vehicle are each rejected with 400 VALIDATION naming the field; the two payments inside the balance are accepted</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Dev (integration, MockMvc + Testcontainers MySQL)</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Dev - xUnit on DealerOps.Core (.NET 10 SDK, no database)</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
           <t>Daniel Watson</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Phase: unit; traces EXT-12</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>IT-03</t>
+          <t>UT-12</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>REQ-AUTH</t>
+          <t>SHOP-01</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>GET /api/vehicles without Authorization header returns 401</t>
+          <t>The buyer-site slug derived from a dealership legal name is stable and collision-free</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Gateway and core running</t>
+          <t>DealerOps.Core builds</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1. GET /api/vehicles without token</t>
+          <t>1. Derive the slug for 'Lakeshore Auto Sales Inc.'
+2. Derive it twice and compare
+3. Derive slugs for two legal names that differ only in punctuation</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>HTTP 401; no vehicle data in body</t>
+          <t>The slug is lower case and URL-safe, identical on repeat, and the two similar names do not produce the same slug</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Dev (integration, MockMvc + Testcontainers MySQL)</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Dev - xUnit on DealerOps.Core (.NET 10 SDK, no database)</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>Daniel Watson</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Phase: unit; traces SHOP-01</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>IT-04</t>
+          <t>IT-01</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>REQ-TENANT</t>
+          <t>AUTH-11, AUTH-12</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>User from Dealer A cannot read Dealer B vehicle by ID</t>
+          <t>Sign in with username, e-mail and phone and receive a JWT carrying the role</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Dealer A and B seeded; vehicle V-B123 belongs to Dealer B</t>
+          <t>E2E stack running; the seeded admin and two dealership staff accounts exist</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1. Login as user-A
-2. GET /api/vehicles/V-B123</t>
+          <t>1. POST /api/v1/auth/login with the username and password
+2. Repeat with the e-mail
+3. Repeat with the phone written with spaces and dashes
+4. Decode the returned token</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>HTTP 404 or 403; no vehicle details for V-B123 returned</t>
+          <t>All three return 200 with a token whose roles claim is Platform.Admin or Dealer.User; the subject is the username</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Dev (integration, MockMvc + Testcontainers MySQL)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>E2E stack - gateway 18080, core 18081, ai-service 8082, MySQL dealer_core_e2e</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
           <t>Daniel Watson</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>Cross-tenant disclosure test</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Phase: integration; traces EXT-07</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>IT-05</t>
+          <t>IT-02</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>REQ-TENANT</t>
+          <t>AUTH-12, AUD-12</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Request body dealerId does not switch tenant context</t>
+          <t>A wrong password is refused and audited as a failed sign-in</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Login as user-A; vehicle V-B123 belongs to Dealer B</t>
+          <t>E2E stack running; staff A exists</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1. POST /api/vehicles with body dealerId=B and target V-B123 fields</t>
+          <t>1. POST /api/v1/auth/login with the right username and a wrong password
+2. Read GET /api/v1/admin/audit filtered by APP_USER as the admin</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400/403; no record created under Dealer B; audit log records attempt</t>
+          <t>401 UNAUTHORIZED with the message 'Invalid sign-in name or password'; one LOGIN_FAILED row under that username with the failure reason and the client IP</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Dev (integration, MockMvc + Testcontainers MySQL)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>E2E stack - gateway 18080, core 18081, ai-service 8082, MySQL dealer_core_e2e</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
           <t>Daniel Watson</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Phase: integration; traces EXT-18</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>IT-06</t>
+          <t>IT-03</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>REQ-INV</t>
+          <t>AUTH-15, AUD-12</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>POST /api/vehicles creates vehicle with status=DRAFT</t>
+          <t>An unknown sign-in identifier is refused without storing what was typed</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Login as admin-A</t>
+          <t>E2E stack running</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1. POST /api/vehicles with valid VIN and vehicle fields</t>
+          <t>1. POST /api/v1/auth/login with an identifier that does not exist
+2. Read the admin audit log filtered by APP_USER</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>HTTP 201; response status=DRAFT; vehicle visible on GET /api/vehicles under Dealer A</t>
+          <t>401 UNAUTHORIZED; one LOGIN_FAILED row by actor anonymous with entity id 0, and the typed identifier appears nowhere in the row</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Dev (integration, MockMvc + Testcontainers MySQL)</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>E2E stack - gateway 18080, core 18081, ai-service 8082, MySQL dealer_core_e2e</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
           <t>Daniel Watson</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="M22" s="2" t="inlineStr"/>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Phase: integration; traces EXT-18</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>IT-07</t>
+          <t>IT-04</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>REQ-INV</t>
+          <t>SEC-02</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>PUT /api/vehicles/{id} on SOLD vehicle returns 409</t>
+          <t>A business endpoint without a token is refused</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Vehicle V-A200 is SOLD</t>
+          <t>E2E stack running</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1. PUT /api/vehicles/V-A200 with price change</t>
+          <t>1. GET /api/v1/vehicles with no Authorization header
+2. Repeat with a token whose signature was altered
+3. Repeat with an expired token</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>HTTP 409 with code=VEHICLE_SOLD_LOCKED; price unchanged in DB</t>
+          <t>All three return 401 UNAUTHORIZED and no vehicle fields</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Dev (integration, MockMvc + Testcontainers MySQL)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>E2E stack - gateway 18080, core 18081, ai-service 8082, MySQL dealer_core_e2e</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
           <t>Daniel Watson</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="M23" s="2" t="inlineStr"/>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Phase: integration; traces FE-01</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>IT-08</t>
+          <t>IT-05</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>REQ-INV</t>
+          <t>AUTH-08</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>POST /api/vehicles with VIN length 16 returns 400 VIN_INVALID</t>
+          <t>The platform admin is refused on every business endpoint</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Login as admin-A</t>
+          <t>E2E stack running; admin token held</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1. POST /api/vehicles with VIN of 16 chars</t>
+          <t>1. GET /api/v1/vehicles, /api/v1/customers, /api/v1/leads and /api/v1/assistant/ask as the admin
+2. Inspect each response body</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400; error code=VIN_INVALID; no record created</t>
+          <t>Each call returns 403 FORBIDDEN and the body carries no VIN, cost or customer field; the admin reads audit only through /api/v1/admin/audit</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Dev (integration, MockMvc + Testcontainers MySQL)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>E2E stack - gateway 18080, core 18081, ai-service 8082, MySQL dealer_core_e2e</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
           <t>Daniel Watson</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Phase: integration; traces BE-13</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>IT-09</t>
+          <t>IT-06</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>REQ-INV</t>
+          <t>AUTH-13</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>POST /api/vehicles/{id}/photos rejects &gt;5MB file</t>
+          <t>A signed-in account with no dealership is refused on business endpoints</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Login as admin-A; vehicle V-A101 in DRAFT</t>
+          <t>E2E stack running; a registered account with no active membership exists</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1. POST photo of 6MB JPEG</t>
+          <t>1. Sign in with that account
+2. GET /api/v1/vehicles
+3. GET /api/v1/me</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>HTTP 413 or 400; code=PHOTO_TOO_LARGE; no photo persisted</t>
+          <t>The business call returns 403 FORBIDDEN (not 401) and /me returns role Dealer.User with dealerId null</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Dev (integration, MockMvc + Testcontainers MySQL)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>E2E stack - gateway 18080, core 18081, ai-service 8082, MySQL dealer_core_e2e</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
           <t>Daniel Watson</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="2" t="inlineStr"/>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="M25" s="2" t="inlineStr"/>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Phase: integration; traces BE-02, EXT-05</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>IT-10</t>
+          <t>IT-07</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>REQ-INV</t>
+          <t>AUTH-07</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>POST /api/vehicles/{id}/photos rejects non-image mime type</t>
+          <t>A resource of another dealership answers 404 for every verb</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Login as admin-A; vehicle V-A101 in DRAFT</t>
+          <t>E2E stack running; staff A and staff B each own at least one vehicle, customer and listing</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1. POST a .exe file as multipart image</t>
+          <t>1. As staff A, GET, PATCH and run a check on dealership B's vehicle, customer and listing ids
+2. Inspect each body</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400; code=PHOTO_UNSUPPORTED_TYPE; no photo persisted</t>
+          <t>Every call returns 404 NOT_FOUND with no VIN, cost or customer field; no call returns 403, so the id cannot be probed</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Dev (integration, MockMvc + Testcontainers MySQL)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>E2E stack - gateway 18080, core 18081, ai-service 8082, MySQL dealer_core_e2e</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
           <t>Daniel Watson</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Phase: integration; traces BE-01, CL-2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>IT-11</t>
+          <t>IT-08</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>REQ-COMP</t>
+          <t>AUTH-09</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>POST /api/listings/{id}/ready without compliance evidence returns 409</t>
+          <t>A spoofed dealerId cannot move a write to another dealership</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Listing L-A1 has no compliance evidence</t>
+          <t>E2E stack running; staff A signed in</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1. POST /api/listings/L-A1/ready</t>
+          <t>1. POST /api/v1/vehicles with dealership B's dealerId in the body
+2. Repeat with it as a query parameter and as a header
+3. Read the created vehicle back as staff A and as staff B</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>HTTP 409; code=COMPLIANCE_REQUIRED; status unchanged</t>
+          <t>The vehicle is written to dealership A in all three attempts; staff B gets 404 for its id</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Dev (integration, MockMvc + Testcontainers MySQL)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>E2E stack - gateway 18080, core 18081, ai-service 8082, MySQL dealer_core_e2e</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
           <t>Daniel Watson</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Phase: integration; traces BE-16</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>IT-12</t>
+          <t>IT-09</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>REQ-COMP</t>
+          <t>DMS-03</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Changing listing price after PASS evidence invalidates readiness</t>
+          <t>A VIN is unique inside a dealership but may repeat across dealerships</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Listing L-A2 has current PASS evidence and status=READY</t>
+          <t>E2E stack running; staff A and staff B signed in</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1. PATCH /api/listings/L-A2 { price: newPrice }
-2. GET /api/listings/L-A2</t>
+          <t>1. As staff A, create a vehicle with a VIN
+2. Create a second vehicle with the same VIN
+3. As staff B, create a vehicle with that same VIN</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Status transitions to NOT_READY with reason=STALE_EVIDENCE</t>
+          <t>The second call returns 400 VIN_DUP and writes no row; staff B's call returns 201</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Dev (integration, MockMvc + Testcontainers MySQL)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>E2E stack - gateway 18080, core 18081, ai-service 8082, MySQL dealer_core_e2e</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
           <t>Daniel Watson</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Phase: integration; traces BE-04</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>IT-13</t>
+          <t>IT-10</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>REQ-COMP</t>
+          <t>DMS-11, DMS-12</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>GET /api/listings/{id}/export returns 409 when NOT_READY</t>
+          <t>Purchase fields are locked after a sale and a vehicle cannot be sold twice</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Listing L-A1 is NOT_READY</t>
+          <t>E2E stack running; an in-stock vehicle with a linked buyer</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1. GET /api/listings/L-A1/export</t>
+          <t>1. POST /api/v1/vehicles/{id}/sell with soldOn and soldPrice
+2. PATCH make, VIN, purchase cost and Carfax URL
+3. Call sell again
+4. Read the row back</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>HTTP 409; code=LISTING_NOT_READY; no export artifact produced</t>
+          <t>The PATCH returns 409 SOLD_LOCKED and the stored purchase values are unchanged; the second sale returns 409 SOLD_LOCKED</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Dev (integration, MockMvc + Testcontainers MySQL)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>E2E stack - gateway 18080, core 18081, ai-service 8082, MySQL dealer_core_e2e</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
           <t>Daniel Watson</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="2" t="inlineStr"/>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="M29" s="2" t="inlineStr"/>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Phase: integration; traces BE-03</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>IT-14</t>
+          <t>IT-11</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>REQ-AI</t>
+          <t>DMS-13</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Ad-check happy path returns PASS verdict with reasons</t>
+          <t>An outdated version on a write is refused</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Listing L-A2 is READY; AI provider stub returns PASS</t>
+          <t>E2E stack running; a vehicle read twice into two clients</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1. POST /api/listings/L-A2/ad-check</t>
+          <t>1. PATCH the vehicle from client 1
+2. PATCH it from client 2 with the version read before that change
+3. Re-read and retry with the current version</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200; verdict=PASS; reasons list present; no secret or PII in response</t>
+          <t>The second write returns 409 VERSION_CONFLICT and changes nothing; the retry with the current version succeeds</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Dev (integration, MockMvc + Testcontainers MySQL)</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>Xiaomei He</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="2" t="inlineStr"/>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>E2E stack - gateway 18080, core 18081, ai-service 8082, MySQL dealer_core_e2e</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>Daniel Watson</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Phase: integration; traces FE-09</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>IT-15</t>
+          <t>IT-12</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>REQ-AI</t>
+          <t>CRM-05, CRM-06, CRM-07, CRM-09</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Ad-check with provider timeout maps to HTTP 504</t>
+          <t>Vehicle-to-customer linking follows the one-vehicle-one-customer rule</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>AI stub configured to delay 20s; AI timeout=2s</t>
+          <t>E2E stack running; dealership A has one unlinked vehicle, one linked vehicle and one customer</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1. POST /api/listings/L-A2/ad-check</t>
+          <t>1. PUT /api/v1/customers/{id}/vehicles/{vehicleId} for the unlinked vehicle
+2. Repeat for the vehicle already linked to another customer
+3. Repeat with dealership B's vehicle id</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>HTTP 504; code=AI_TIMEOUT; no partial verdict stored</t>
+          <t>200 for the free vehicle; 409 VEHICLE_ALREADY_LINKED for the taken one; 404 NOT_FOUND for the other dealership's id</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Dev (integration, MockMvc + Testcontainers MySQL)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>Xiaomei He</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr"/>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>E2E stack - gateway 18080, core 18081, ai-service 8082, MySQL dealer_core_e2e</t>
+        </is>
+      </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>Failure-safe behavior</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+          <t>Daniel Watson</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Phase: integration; traces BE-05</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>IT-16</t>
+          <t>IT-13</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>REQ-AI</t>
+          <t>CRM-08, CRM-11</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Direct call to ai-service port 8082 from outside is blocked</t>
+          <t>A sold vehicle cannot be unlinked and an in-stock unlink is audited</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>ai-service running; firewall rules applied</t>
+          <t>E2E stack running; one sold linked vehicle and one in-stock linked vehicle</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1. From external host, curl http://host:8082/api/ai/health</t>
+          <t>1. DELETE the link on the sold vehicle
+2. DELETE the link on the in-stock vehicle
+3. Read the customer audit history as the manager</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Connection refused or 403; no response body from ai-service</t>
+          <t>The sold link returns 409 SOLD_LOCKED and survives; the in-stock link returns 204 and writes an UNLINK audit row</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Dev (integration, MockMvc + Testcontainers MySQL)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>Xiaomei He</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr"/>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>E2E stack - gateway 18080, core 18081, ai-service 8082, MySQL dealer_core_e2e</t>
+        </is>
+      </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>Internal-only enforcement</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+          <t>Daniel Watson</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Phase: integration; traces BE-06</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>IT-17</t>
+          <t>IT-14</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>REQ-GW</t>
+          <t>AD-07</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Gateway health endpoint returns 200 and status=UP</t>
+          <t>A hard rule hit returns BLOCKED and does not call the AI service</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Gateway running</t>
+          <t>E2E stack running; a draft ad for an in-stock vehicle; ai-service log tailed</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1. GET /actuator/health</t>
+          <t>1. Save a CASH body with no price
+2. POST /api/v1/listings/{id}/checks
+3. Read the response and the ai-service log
+4. Change to FINANCE with a price but no APR and check again</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200; status=UP; subcomponents listed</t>
+          <t>Both checks return HTTP 200 with recommendation BLOCKED and aiStatus SKIPPED; the ai-service log shows no /internal/v1/ad-check call</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Dev (integration, MockMvc + Testcontainers MySQL)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>Daniel Watson</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr"/>
-      <c r="L33" s="2" t="inlineStr"/>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>E2E stack - gateway 18080, core 18081, ai-service 8082, MySQL dealer_core_e2e</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>Xiaomei He</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Minor</t>
+          <t>Phase: integration; traces BE-09, CL-4</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>IT-18</t>
+          <t>IT-15</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>REQ-GW</t>
+          <t>AD-08, AI-01</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Gateway rejects request with forged X-Dealer-Internal header</t>
+          <t>A compliant ad reaches the real AI review and is stored as passed</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>User-A logged in</t>
+          <t>E2E stack running with AIMANAGER_API_KEY configured; a complete CASH ad body</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1. GET /api/vehicles with header X-Dealer-Internal: 1</t>
+          <t>1. POST /api/v1/listings/{id}/checks
+2. Wait for the response (limit 15 s)
+3. GET the listing and read the stored check</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400 or header stripped; request routed normally with user's own dealerId</t>
+          <t>200 with recommendation PASSED, aiStatus not SKIPPED, AI notes present but not blocking, and the stored check carries the checked content version and time</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Dev (integration, MockMvc + Testcontainers MySQL)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>Daniel Watson</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr"/>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>E2E stack - gateway 18080, core 18081, ai-service 8082, MySQL dealer_core_e2e</t>
+        </is>
+      </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>Boundary spoofing attempt</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+          <t>Xiaomei He</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Phase: integration; traces CL-5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>IT-19</t>
+          <t>IT-16</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>REQ-CRM</t>
+          <t>AD-09, AI-02</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Customer creation records audit entry with actor and dealerId</t>
+          <t>An AI timeout or failure is stored as unavailable and is never a pass</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Login as admin-A</t>
+          <t>E2E stack running; ai-service stopped or its key removed</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1. POST /api/customers { name, email }
-2. GET /api/audit?entity=customer</t>
+          <t>1. Run a check on an ad that passes the fixed rules
+2. Read the response
+3. GET the listing again</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Customer created under Dealer A; audit entry contains actor=admin-A, dealerId=A, action=CREATE</t>
+          <t>502 AI_UNAVAILABLE; the compliance_check row is already written with recommendation UNAVAILABLE and the listing reads back as AI_UNAVAILABLE, never PASSED</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Dev (integration, MockMvc + Testcontainers MySQL)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>Daniel Watson</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr"/>
-      <c r="L35" s="2" t="inlineStr"/>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>E2E stack - gateway 18080, core 18081, ai-service 8082, MySQL dealer_core_e2e</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>Xiaomei He</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Phase: integration; traces BE-08</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>IT-20</t>
+          <t>IT-17</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>REQ-CRM</t>
+          <t>AD-12, AD-13</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Work order linked to another dealer's customer is rejected</t>
+          <t>Ready and export are reachable only from a pass on the current content version</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Login as admin-A; customer C-B500 belongs to Dealer B</t>
+          <t>E2E stack running; one listing in each of blocked, needs-AI, passed and stale state</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1. POST /api/work-orders { customerId: 'C-B500' }</t>
+          <t>1. Call ready and export on the blocked, needs-AI and unavailable listings
+2. Mark the passed listing ready and export it
+3. Edit the price in the body and call ready and export again</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>HTTP 400/403; code=TENANT_MISMATCH; no work order created</t>
+          <t>The first group returns 409 NOT_PASSED; the passed listing returns 200 and a text/plain file with no purchase cost and no customer data; after the edit both calls return 409 CHECK_STALE</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Dev (integration, MockMvc + Testcontainers MySQL)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>Daniel Watson</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr"/>
-      <c r="L36" s="2" t="inlineStr"/>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>E2E stack - gateway 18080, core 18081, ai-service 8082, MySQL dealer_core_e2e</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>Xiaomei He</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Phase: integration; traces BE-07, BE-10, CL-6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>SYS-01</t>
+          <t>IT-18</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>REQ-INV</t>
+          <t>SEC-02, SEC-05</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>End-to-end: create vehicle via web, verify in list, edit, sell, confirm locked</t>
+          <t>Core and ai-service are not reachable without the internal token and the gateway never forwards it</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>dealer-web served through gateway; admin-A logged in</t>
+          <t>E2E stack running</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1. Click 'Add vehicle' and submit form
-2. Verify vehicle appears in inventory list
-3. Edit price and save
-4. Mark vehicle SOLD
-5. Attempt second edit</t>
+          <t>1. GET http://127.0.0.1:18081/api/v1/vehicles with a valid user JWT but no internal header
+2. GET http://127.0.0.1:8082/internal/v1/ad-check
+3. Send /api/v1/vehicles through the gateway with a forged X-Dealer-Internal header</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Vehicle created; edits persist; sold transition succeeds; subsequent edit UI shows locked and API rejects</t>
+          <t>The two direct calls return 404; the forged header is stripped or refused and the request is authorised by the user JWT alone</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Staging (gateway 8080 + core 8081 + ai 8082 + dealer-web)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>E2E stack - gateway 18080, core 18081, ai-service 8082, MySQL dealer_core_e2e</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
           <t>Daniel Watson</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr"/>
-      <c r="L37" s="2" t="inlineStr"/>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Phase: integration; traces BE-14</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>SYS-02</t>
+          <t>IT-19</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>REQ-INV</t>
+          <t>DMS-08, AD-17</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Upload a photo, verify preview and persistence after refresh</t>
+          <t>Photo upload enforces type, size and count limits per vehicle</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Vehicle V-A101 in DRAFT; user admin-A logged in</t>
+          <t>E2E stack running; an in-stock vehicle; fixture images prepared</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1. Open vehicle detail
-2. Upload a 2MB JPEG
-3. Refresh page</t>
+          <t>1. Upload a 1 MB JPEG and a PNG
+2. Upload a 3 MB JPEG
+3. Upload a text file renamed to .jpg
+4. Upload an eleventh photo</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Photo preview shows; thumbnail persists after refresh; stored copy retrievable via API</t>
+          <t>The first two return 201; 3 MB returns the 2 MB limit message; the fake JPEG returns 415 UNSUPPORTED_MEDIA_TYPE; the eleventh returns 400</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Staging (gateway 8080 + core 8081 + ai 8082 + dealer-web)</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>E2E stack - gateway 18080, core 18081, ai-service 8082, MySQL dealer_core_e2e</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
           <t>Daniel Watson</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="2" t="inlineStr"/>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="M38" s="2" t="inlineStr"/>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Phase: integration; traces EXT-08</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>SYS-03</t>
+          <t>IT-20</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>REQ-COMP</t>
+          <t>PAY-01, PAY-03, PAY-05</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>End-to-end listing workflow: compliance pass → Ready → export</t>
+          <t>The payment ledger enforces the balance and the manager-only reads</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Listing L-A2 with vehicle data populated</t>
+          <t>E2E stack running; a vehicle sold for 21,000; one manager and one staff account</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1. Trigger compliance check
-2. Verify PASS banner
-3. Click 'Mark Ready'
-4. Click 'Export'</t>
+          <t>1. As staff, POST a payment of 6,000, then one of 25,000
+2. As staff, GET the ledger and DELETE a payment
+3. As the manager, GET the ledger and DELETE the 6,000 payment</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Readiness check PASS; Ready status set; export generates artifact and recorded in listing history</t>
+          <t>6,000 returns 201 with the payment item only; 25,000 returns 400 VALIDATION; both staff reads return 403 FORBIDDEN; the manager sees soldPrice, paidTotal and balanceDue and the delete soft-deletes the row and writes an audit entry</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Staging (gateway 8080 + core 8081 + ai 8082 + dealer-web)</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>E2E stack - gateway 18080, core 18081, ai-service 8082, MySQL dealer_core_e2e</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
           <t>Daniel Watson</t>
         </is>
       </c>
-      <c r="K39" s="2" t="inlineStr"/>
-      <c r="L39" s="2" t="inlineStr"/>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Phase: integration; traces EXT-12, EXT-19</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>SYS-04</t>
+          <t>IT-21</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>REQ-AI</t>
+          <t>SHOP-02, SHOP-03, SHOP-04, SHOP-05</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Ad-check fail-safe when AI provider is unreachable</t>
+          <t>The public buyer-site API exposes only listed vehicles and files an inquiry as a lead</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>ai-service configured with unreachable provider; listing L-A2 Ready</t>
+          <t>E2E stack running; one vehicle ready with a passed check and one that is not</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1. Click 'Run ad check' in UI
-2. Wait for completion</t>
+          <t>1. GET /api/v1/public/dealers/{slug}/inventory with no token
+2. Request the photo of the unlisted vehicle
+3. POST an inquiry for the listed vehicle
+4. POST six inquiries from one IP inside a minute</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>UI shows 'AI unavailable' banner; no false PASS stored; export button not enabled by AI result</t>
+          <t>The inventory is anonymous and carries no VIN, cost, list price or customer data; the unlisted photo returns 404; the inquiry creates or reuses a customer and files a NEW lead with the message as its first note; the sixth inquiry is rate-limited</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Staging (gateway 8080 + core 8081 + ai 8082 + dealer-web)</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>E2E stack - gateway 18080, core 18081, ai-service 8082, MySQL dealer_core_e2e</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
           <t>Daniel Watson</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr"/>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>Failure-safe UI latch</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Phase: integration; traces EXT-14, EXT-15</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>SYS-05</t>
+          <t>IT-22</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>REQ-GW</t>
+          <t>AUD-10, AUD-11, AUD-17</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Browser can only reach gateway (8080); direct 8081/8082 blocked</t>
+          <t>Audit reads are limited to the right role and dealership</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Services running on their own ports</t>
+          <t>E2E stack running; staff, manager and admin accounts; recent business writes present</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1. Open browser devtools and attempt fetch to http://host:8081/api/vehicles
-2. Attempt fetch to http://host:8082/api/ai/health</t>
+          <t>1. As staff, GET /api/v1/audit and /api/v1/dealer/audit
+2. As a dealer user, GET /api/v1/admin/audit
+3. As the manager, filter /api/v1/dealer/audit by VEHICLE
+4. As the admin, filter /api/v1/admin/audit by dealership</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Both direct calls fail (CORS or connection); only gateway responds on 8080</t>
+          <t>Both staff calls and the dealer user's platform-log call return 403 FORBIDDEN; the manager sees only this dealership's rows newest first; the admin sees every dealership with the dealership column</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Staging (gateway 8080 + core 8081 + ai 8082 + dealer-web)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>Daniel Watson</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="2" t="inlineStr"/>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>E2E stack - gateway 18080, core 18081, ai-service 8082, MySQL dealer_core_e2e</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>Xiaomei He</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Phase: integration; traces EXT-17</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>SYS-06</t>
+          <t>IT-23</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>REQ-CRM</t>
+          <t>CRM-15</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Audit trail: user action logged with user, dealer, timestamp</t>
+          <t>Lead lifecycle rules hold and a closed lead stops accepting changes</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>admin-A logged in</t>
+          <t>E2E stack running; dealership A has an in-stock vehicle</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1. Create customer
-2. Open audit log page
-3. Filter by today's date</t>
+          <t>1. Create a lead with a new customer, an owner and a note
+2. Set CONTACTED with a past follow-up date
+3. Set LOST with no reason, then with a reason
+4. PATCH the lead again and add a note</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Audit entry visible with actor=admin-A, dealerId=A, action=CREATE, timestamp within last minute</t>
+          <t>The lead and customer are created and the note is visible; the overdue filter returns the lead; LOST without a reason is refused; after it closes a PATCH returns 409 LEAD_CLOSED while a note is still accepted</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Staging (gateway 8080 + core 8081 + ai 8082 + dealer-web)</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>E2E stack - gateway 18080, core 18081, ai-service 8082, MySQL dealer_core_e2e</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
           <t>Daniel Watson</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="2" t="inlineStr"/>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Phase: integration; traces EXT-02, EXT-03</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>SYS-07</t>
+          <t>IT-24</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>REQ-WEB</t>
+          <t>WO-08</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Session expiry: expired JWT prompts re-login and preserves destination</t>
+          <t>Work orders block a sale while open and settle their cost when done</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>admin-A logged in with JWT expiring in 10 seconds</t>
+          <t>E2E stack running; an in-stock vehicle with no work orders</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1. Wait 15 seconds
-2. Click inventory menu</t>
+          <t>1. Add a work order with an assignee and start it
+2. Try to sell the vehicle
+3. Complete the order with a note and cost 150
+4. PATCH the completed order, then sell, then add an order to the sold vehicle</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Request returns 401; UI redirects to login; after login, returns to inventory page</t>
+          <t>The sale returns 409 WORK_ORDERS_OPEN; completion raises repairCost by 150 with a VEHICLE UPDATE audit row; the PATCH returns 409 WORK_ORDER_CLOSED; the sale then succeeds and the new order returns 409 SOLD_LOCKED</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>Staging (gateway 8080 + core 8081 + ai 8082 + dealer-web)</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>E2E stack - gateway 18080, core 18081, ai-service 8082, MySQL dealer_core_e2e</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
           <t>Daniel Watson</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="2" t="inlineStr"/>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Phase: integration; traces EXT-04</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>SYS-08</t>
+          <t>IT-25</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>REQ-WEB</t>
+          <t>AI-03, AI-04</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>UI shows read-only banner when viewing SOLD vehicle</t>
+          <t>The assistant answers read-only inside one dealership and degrades safely</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Vehicle V-A200 is SOLD; admin-A logged in</t>
+          <t>E2E stack running; staff A, the admin and seeded inventory</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1. Open V-A200 detail page</t>
+          <t>1. As staff A, POST /api/v1/assistant/ask with a make that matches several vehicles
+2. Inspect the cards and compare the ids with dealership A's data
+3. Call the same URL as the admin
+4. Stop the AI provider and ask again</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Edit controls disabled; banner reads 'Vehicle sold — read only'; save button hidden</t>
+          <t>At most five cards, all from dealership A, with no purchase cost or contact data and no write to any business table; the admin receives 403; with the provider down the call returns 200 with summaryAvailable false</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Staging (gateway 8080 + core 8081 + ai 8082 + dealer-web)</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>Daniel Watson</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="2" t="inlineStr"/>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>E2E stack - gateway 18080, core 18081, ai-service 8082, MySQL dealer_core_e2e</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>Xiaomei He</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Minor</t>
+          <t>Phase: integration; traces BE-12, FE-10</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>SYS-09</t>
+          <t>IT-26</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>REQ-WEB</t>
+          <t>DMS-04, SEC-02</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Form validation surfaces API error codes to user clearly</t>
+          <t>VIN decode is public, validated and does not expose inventory</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>admin-A logged in; VIN length 16</t>
+          <t>E2E stack running; vPIC reachable or its snapshot in use</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>1. Submit vehicle form with 16-char VIN</t>
+          <t>1. GET /api/v1/catalog/vin/1HGCM82633A004352 with no token
+2. Repeat with a VIN containing I
+3. GET /api/v1/vehicles with no token</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Form shows inline error 'VIN must be 17 characters'; no vehicle created</t>
+          <t>The decode returns make, model and year as reference facts and stores nothing; the invalid VIN returns a field error; the inventory call returns 401</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Staging (gateway 8080 + core 8081 + ai 8082 + dealer-web)</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>E2E stack - gateway 18080, core 18081, ai-service 8082, MySQL dealer_core_e2e</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
           <t>Daniel Watson</t>
         </is>
       </c>
-      <c r="K45" s="2" t="inlineStr"/>
-      <c r="L45" s="2" t="inlineStr"/>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Minor</t>
+          <t>Phase: integration; traces EXT-01</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>SYS-10</t>
+          <t>SYS-01</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>REQ-WEB</t>
+          <t>AUTH-01, AUTH-08</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Logout clears session and token from browser storage</t>
+          <t>Route guards send each role to its own area in the browser</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>admin-A logged in</t>
+          <t>E2E stack running; admin, manager and staff accounts</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>1. Click 'Logout'
-2. Inspect browser localStorage / sessionStorage</t>
+          <t>1. Open /dms signed out
+2. Sign in as the admin and open /dms, /crm, /leads and /ads
+3. Sign in as staff A and open /admin
+4. Read the menu in each case</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>No access token or dealer context remaining; next API call returns 401</t>
+          <t>Signed out goes to /login; the admin is returned to /admin with no vehicle table rendered; staff are returned to /dms with no dealership table; each menu lists only that role's pages</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Staging (gateway 8080 + core 8081 + ai 8082 + dealer-web)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>E2E stack - Chromium on http://localhost:5175 through gateway 18080</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
           <t>Daniel Watson</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="2" t="inlineStr"/>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="M46" s="2" t="inlineStr"/>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Phase: system; traces FE-01 to FE-06</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>AT-01</t>
+          <t>SYS-02</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>REQ-AUTH</t>
+          <t>AUTH-06, AUTH-07, CRM-05</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Dealer admin signs in and sees own dealership context</t>
+          <t>One dealership records a vehicle and a customer, links them, and the other sees nothing</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Admin credentials for Dealer A on hand</t>
+          <t>E2E stack running; two dealerships with one staff account each</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>1. Navigate to login page
-2. Enter admin credentials
-3. Observe landing dashboard</t>
+          <t>1. As staff A add a vehicle on /dms and a customer on /crm, then link them
+2. Sign out and sign in as staff B; open /dms and /crm
+3. As staff B open /dms?vehicleId=&lt;dealership A id&gt;</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Admin lands on dashboard displaying 'Dealer A' context and admin menu</t>
+          <t>Staff A sees the linked vehicle on the customer row; staff B sees only their own data and the deep link shows 'Vehicle not found' rather than dealership A's fields</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>Staging (acceptance walkthrough with synthetic dealership data)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>E2E stack - Chromium on http://localhost:5175 through gateway 18080</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
           <t>Daniel Watson</t>
         </is>
       </c>
-      <c r="K47" s="2" t="inlineStr"/>
-      <c r="L47" s="2" t="inlineStr"/>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="M47" s="2" t="inlineStr"/>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Phase: system; traces CL-2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>AT-02</t>
+          <t>SYS-03</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>REQ-TENANT</t>
+          <t>DMS-06, DMS-07, AUD-15</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Dealer A user cannot see Dealer B listings anywhere in UI</t>
+          <t>The inventory list pages, searches and filters correctly and stays newest first</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Dealer A user logged in; Dealer B has listings</t>
+          <t>E2E stack running; the demo seed loaded (at least 30 vehicles in the dealership)</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1. Open inventory, listings, customers, audit pages
-2. Search for Dealer B VINs or names</t>
+          <t>1. Open /dms and read the first page
+2. Page forward and back
+3. Search a VIN fragment, a make and a stock number
+4. Filter by status and by condition</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>No Dealer B records visible or searchable; API audit shows no cross-tenant read attempt succeeded</t>
+          <t>Ten rows per page, newest first, stable paging, and each search or filter returns only matching rows with an explicit empty state when nothing matches</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Staging (acceptance walkthrough with synthetic dealership data)</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>E2E stack - Chromium on http://localhost:5175 through gateway 18080</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
           <t>Daniel Watson</t>
         </is>
       </c>
-      <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="2" t="inlineStr"/>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Phase: system; traces DMS-06, DMS-07</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>AT-03</t>
+          <t>SYS-04</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>REQ-COMP</t>
+          <t>AD-07</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Listing cannot be exported without current PASSED compliance</t>
+          <t>A blocked ad is shown as blocked and the browser makes no AI call</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Listing L-A3 with stale evidence</t>
+          <t>E2E stack running; the browser network panel open</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>1. Open listing L-A3
-2. Attempt to export</t>
+          <t>1. Open /ads and select a vehicle with no listing
+2. Write a CASH body with no price and save the draft
+3. Run the check and read the right pane and the network panel</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Export button disabled or export API returns 409; user sees reason 'Compliance evidence stale'</t>
+          <t>The right pane shows Blocked with the price finding, the request returns 200, and no request to /internal/v1/ad-check appears in the network panel</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>Staging (acceptance walkthrough with synthetic dealership data)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>Daniel Watson</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr"/>
-      <c r="L49" s="2" t="inlineStr"/>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>E2E stack - Chromium on http://localhost:5175 through gateway 18080</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>Xiaomei He</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Phase: system; traces CL-4</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>AT-04</t>
+          <t>SYS-05</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>REQ-AI</t>
+          <t>AD-08, AD-09</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Ad check never reports PASS when provider is unavailable</t>
+          <t>A compliant ad passes and an AI outage is shown as unavailable, not as a pass</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>AI provider offline</t>
+          <t>E2E stack running with the AI key configured</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>1. Run ad check on listing L-A2</t>
+          <t>1. Write a complete CASH body and run the check
+2. Stop the AI service and run the check again
+3. Read the right pane and the Mark ready button in both cases</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Verdict shown as 'Unavailable, try later'; no PASS recorded in listing history</t>
+          <t>The first run shows Passed within 15 s with AI notes; the second shows 'AI unavailable', keeps the check row and leaves Mark ready and Export refused</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Staging (acceptance walkthrough with synthetic dealership data)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>Daniel Watson</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr"/>
-      <c r="L50" s="2" t="inlineStr"/>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>E2E stack - Chromium on http://localhost:5175 through gateway 18080</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>Xiaomei He</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Phase: system; traces CL-5</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>AT-05</t>
+          <t>SYS-06</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>REQ-CRM</t>
+          <t>AD-11, AD-12, AD-14</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Audit log can be filtered by user and action for compliance review</t>
+          <t>Editing a passed ad makes it stale and stops the export</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>At least 10 audit records exist for Dealer A</t>
+          <t>E2E stack running; a listing that has just passed</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>1. Open audit page
-2. Filter by actor=admin-A and action=UPDATE</t>
+          <t>1. Mark the listing ready and export the TXT file
+2. Change the price digits in the body and save
+3. Click Mark ready and Export again
+4. Open the disclaimer link in the result panel</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Filtered list shows only matching records; export CSV contains filtered rows only</t>
+          <t>The first export downloads plain text with the dealership and public vehicle fields only; after the edit the pane shows Stale and both actions report 'Check is stale. Run check again'; the disclaimer page states the check is not OMVIC approval</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>Staging (acceptance walkthrough with synthetic dealership data)</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>Daniel Watson</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr"/>
-      <c r="L51" s="2" t="inlineStr"/>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>E2E stack - Chromium on http://localhost:5175 through gateway 18080</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>Xiaomei He</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Phase: system; traces CL-6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>AT-06</t>
+          <t>SYS-07</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>REQ-WEB</t>
+          <t>DMS-10, PAY-01, SALE-01</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Full lifecycle: create vehicle, add photo, compliance check, mark ready, export</t>
+          <t>Selling a vehicle, recording payments and printing the bill of sale works end to end</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>admin-A logged in; fresh VIN available</t>
+          <t>E2E stack running; an in-stock vehicle and a customer</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>1. Create vehicle → upload photo → set price → run compliance → mark ready → export</t>
+          <t>1. Sell the vehicle for 21,000 and name the buyer from CRM
+2. Record payments of 6,000 and 15,000
+3. Remove one payment as the manager
+4. Open /dms/{id}/bill-of-sale and print to PDF</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>All steps succeed; export artifact lists correct vehicle data and compliance evidence ID</t>
+          <t>The sale links the buyer, the balance moves 15,000 -&gt; 0 -&gt; 15,000, the removal is audited, and the bill of sale prints the dealer, buyer, vehicle, payments and balance without the application chrome</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>Staging (acceptance walkthrough with synthetic dealership data)</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>E2E stack - Chromium on http://localhost:5175 through gateway 18080</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
           <t>Daniel Watson</t>
         </is>
       </c>
-      <c r="K52" s="2" t="inlineStr"/>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>Golden path</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="M52" s="2" t="inlineStr"/>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Phase: system; traces EXT-12</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>AT-07</t>
+          <t>SYS-08</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>REQ-WEB</t>
+          <t>DASH-01, CRM-16, WO-08</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Non-admin user cannot access admin-only menus</t>
+          <t>The dashboard and reports agree with the underlying report endpoints</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Regular sales user for Dealer A logged in</t>
+          <t>E2E stack running; seeded sales, leads and a completed work order with cost 120.50</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>1. Attempt to open 'Users' and 'Audit' menus</t>
+          <t>1. Open /dashboard and record every KPI
+2. Open the sales and funnel reports
+3. Call the three report endpoints directly and compare the numbers</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Menus hidden; direct URL access returns 403; no admin data leaked</t>
+          <t>Each KPI matches the endpoint value, the workshop settlement shows 120.50 by month and assignee, and the funnel shows this month's stage entries</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr"/>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>Staging (acceptance walkthrough with synthetic dealership data)</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>Daniel Watson</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr"/>
-      <c r="L53" s="2" t="inlineStr"/>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>E2E stack - Chromium on http://localhost:5175 through gateway 18080</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>Yuandong Yang</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Phase: system; traces EXT-13</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>AT-08</t>
+          <t>SYS-09</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>REQ-WEB</t>
+          <t>SHOP-01, SHOP-04</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Error messages are user-readable and do not leak stack traces</t>
+          <t>The public buyer site lists ready ads and an inquiry reaches the dealership inbox</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>admin-A logged in</t>
+          <t>E2E stack running; one ad ready and passed; a second browser profile signed out</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>1. Trigger validation failure (bad VIN)
-2. Trigger 409 (sold vehicle edit)</t>
+          <t>1. Open /shop and then /shop/{slug} signed out
+2. Submit an empty inquiry, then a complete one
+3. Sign in as the dealership staff and open the header inbox
+4. Sell the listed vehicle and reload /shop/{slug}</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Both show business-friendly messages; no Java stack trace, no SQL, no secret in UI or network body</t>
+          <t>The listed vehicle appears without VIN or cost; the empty form shows field errors; the complete form files a NEW lead visible in the inbox with an Open lead link; after the sale the vehicle leaves the public inventory</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>Staging (acceptance walkthrough with synthetic dealership data)</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>E2E stack - Chromium on http://localhost:5175 through gateway 18080</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
           <t>Daniel Watson</t>
         </is>
       </c>
-      <c r="K54" s="2" t="inlineStr"/>
-      <c r="L54" s="2" t="inlineStr"/>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="M54" s="2" t="inlineStr"/>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Phase: system; traces EXT-14, EXT-15</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>AT-09</t>
+          <t>SYS-10</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>REQ-WEB</t>
+          <t>AUD-17, PAY-05</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Browser compatibility: workflow succeeds in Chrome and one other Chromium browser</t>
+          <t>A manager and a staff member see different team, audit and ledger surfaces</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Two supported browsers installed</t>
+          <t>E2E stack running; one manager and one staff account in the same dealership</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>1. Repeat AT-06 in Chrome
-2. Repeat in secondary browser</t>
+          <t>1. Sign in as the manager and open /team, the audit log and a sold vehicle drawer
+2. Sign in as the staff member and open the same pages and drawer
+3. Watch the browser console in both runs</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Both complete without layout break or console error</t>
+          <t>Only the manager sees Team, the dealership audit log, the record history and the payment ledger; the staff drawer shows the record-payment form only, and neither session logs a 403 in the console</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>Staging (acceptance walkthrough with synthetic dealership data)</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>E2E stack - Chromium on http://localhost:5175 through gateway 18080</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
           <t>Daniel Watson</t>
         </is>
       </c>
-      <c r="K55" s="2" t="inlineStr"/>
-      <c r="L55" s="2" t="inlineStr"/>
-      <c r="M55" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="M55" s="2" t="inlineStr"/>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Minor</t>
+          <t>Phase: system; traces EXT-16, EXT-19</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>AT-10</t>
+          <t>SYS-11</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>REQ-WEB</t>
+          <t>AD-09, AI-05</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>After acceptance run, no real customer PII exists in test data or evidence</t>
+          <t>Loading, empty, error and AI-failure states are explicit on every page</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Evidence folder for this acceptance run available</t>
+          <t>E2E stack running; core reachable, then stopped on purpose</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>1. Grep evidence for real email domains outside test allowlist
-2. Review screenshots for PII</t>
+          <t>1. Walk /dms, /crm, /leads, /ads and the assistant with an empty dealership
+2. Stop core and repeat the walk
+3. Ask the assistant while the AI provider is down</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>No real PII detected; test data uses synthetic names/emails/VINs only</t>
+          <t>Each page shows its own loading, empty and failure copy ('No vehicles match.', 'Could not load vehicles.'); a 403 or 502 is never painted as an empty table; the assistant shows 'Smart summary unavailable' with its cards still listed</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr"/>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Pass/Fail</t>
+          <t>Not executed (planned)</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Staging (acceptance walkthrough with synthetic dealership data)</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>E2E stack - Chromium on http://localhost:5175 through gateway 18080</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>Daniel Watson</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>Phase: system; traces FE-09, FE-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>SYS-12</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>SEC-02</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>An expired session and a sign-out leave no usable credentials in the browser</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>E2E stack running; a short-lived token configured for the run</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>1. Sign in and wait for the token to expire, then click a business action
+2. Sign in again and sign out
+3. Inspect local and session storage and press Back
+4. Repeat the walk at phone width</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>The expired session returns to /login without exposing data; after sign-out no token remains in storage and Back does not restore a signed-in page; the phone-width walk shows the same guards</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>Not executed (planned)</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>E2E stack - Chromium on http://localhost:5175 through gateway 18080</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>Daniel Watson</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>Phase: system; regression bundle and roles walk</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>AT-01</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>AUTH-02, AUTH-03, AUTH-14</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Classroom script 1: the admin opens two dealerships and binds one person to each</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Azure demo deployed; admin credentials ready</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>1. Sign in as the admin on the cloud URL and land on /admin
+2. Create dealership A and dealership B with all four contact fields
+3. Bind staff A and staff B with a username, display name and temporary password
+4. Bind staff A again</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Both dealerships and both bindings are created and listed on the Members tab; the repeated binding shows 'Staff already bound' (409 DUP_MEMBER) instead of a second row; the admin menu shows no business pages</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>Not executed (planned)</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>Azure demo - https://dealer-ops-dev.azurewebsites.net (cloud HTTPS, real AI)</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
           <t>Yuandong Yang</t>
         </is>
       </c>
-      <c r="K56" s="2" t="inlineStr"/>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>Pre-submission scrub</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr">
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>Phase: acceptance; classroom script CL-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>AT-02</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>AUTH-07, AUTH-08</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Classroom script 2 and 3: isolation in the browser and the admin refused at the API</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>AT-01 complete; both staff accounts signed in on the cloud</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>1. As staff A record a vehicle and a customer and link them
+2. As staff B open /dms and /crm
+3. With the admin token call GET /api/v1/vehicles from a terminal</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Staff B sees none of dealership A's data; the admin call returns 403 FORBIDDEN with no business fields, so the isolation evidence is not 'the button was hidden'</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Not executed (planned)</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N56" s="2" t="inlineStr">
+      <c r="J59" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>Azure demo - https://dealer-ops-dev.azurewebsites.net (cloud HTTPS, real AI)</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>Yuandong Yang</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>Phase: acceptance; classroom scripts CL-2 and CL-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>AT-03</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>AD-07</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Classroom script 4: a missing price and a missing APR stay blocked in the cloud</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Cloud demo signed in as staff A with a vehicle recorded</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>1. Write a CASH ad with no price and run the check
+2. Switch to FINANCE, add a price but no APR, and run it again
+3. Watch the network panel throughout</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Both runs return Blocked with their reason codes, the request succeeds with 200, and no AI call is made from either run</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Not executed (planned)</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>Azure demo - https://dealer-ops-dev.azurewebsites.net (cloud HTTPS, real AI)</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>Xiaomei He</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>Phase: acceptance; classroom script CL-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>AT-04</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>AD-08, AI-01, AI-02</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Classroom script 5: real AI reviews a compliant ad once, within the timeout</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Cloud demo with the real provider key in Key Vault</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>1. Write a compliant CASH body with the dealership name, contact, price, condition wording and year
+2. Run the check and time the response
+3. Read the AI notes and the stored check</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>The result is Passed within 15 s, aiStatus is not SKIPPED, the notes may list risks without blocking, and a provider outage would instead show 'AI unavailable'</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Not executed (planned)</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>Azure demo - https://dealer-ops-dev.azurewebsites.net (cloud HTTPS, real AI)</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>Xiaomei He</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>Phase: acceptance; classroom script CL-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>AT-05</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>AD-11, AD-12</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Classroom script 6: after a price change the old pass cannot export</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>AT-04 complete and the listing marked ready</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>1. Export the TXT file while the check is current
+2. Change the price digits in the body and save
+3. Click Mark ready and Export again
+4. Re-run the check and export once it passes again</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>The first export succeeds with no purchase cost or customer data; after the edit both actions report the stale check; only a fresh pass on the current version allows the export again</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>Not executed (planned)</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>Azure demo - https://dealer-ops-dev.azurewebsites.net (cloud HTTPS, real AI)</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>Xiaomei He</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>Phase: acceptance; classroom script CL-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>AT-06</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>AUD-10, AUD-11, AUD-17, CRM-12</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Audit walkthrough for the manager and the admin with no contact leakage outside the trail</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Cloud demo with recent business writes by staff A</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>1. As staff A edit a vehicle price, edit an ad, run a check and export
+2. As the manager open the dealership audit log and filter by VEHICLE and LISTING
+3. As the admin open the platform log and filter by dealership
+4. As staff open the same log URLs</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Rows are newest first and show who, what, when, the source IP and the replaced value; the admin log adds the dealership; staff receive 403; no AI prompt, log file or assistant answer contains a customer phone, e-mail or address</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>Not executed (planned)</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>Azure demo - https://dealer-ops-dev.azurewebsites.net (cloud HTTPS, real AI)</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>Xiaomei He</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>Phase: acceptance; traces EXT-17, BE-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>AT-07</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>AUTH-01, AD-16</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Client and instructor walkthrough of the agreed demo set with sign-off</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>All earlier acceptance cases executed; client representative or instructor present</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>1. Walk the client through sign-in, DMS, CRM, the three ad kinds, export, the buyer site and the dashboard on the cloud
+2. Record every question, deferral and defect raised
+3. Collect the walkthrough sign-off or the explicit deferrals</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>The client confirms the demonstrated behaviour or records deferrals in writing; marketplace publishing is presented as a labelled simulation, not as a real listing</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>Not executed (planned)</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>Azure demo - https://dealer-ops-dev.azurewebsites.net (cloud HTTPS, real AI)</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>Yuandong Yang</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>Phase: acceptance; customer walkthrough</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>AT-08</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>SEC-04, CRM-12</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Privacy and secret scrub of the evidence set before submission</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>All execution evidence collected in the evidence folder</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>1. Search every screenshot, log excerpt and exported file for real customer data
+2. Search the same set for keys, tokens, connection strings and passwords
+3. Confirm each dataset came from the synthetic seed
+4. Quarantine and regenerate anything that fails</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>No real customer contact data and no secret value remains in the evidence; every artefact is traceable to the synthetic seed</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>Not executed (planned)</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>Azure demo - https://dealer-ops-dev.azurewebsites.net (cloud HTTPS, real AI)</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>Yuandong Yang</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>Phase: acceptance; privacy gate before hand-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>DEP-01</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>SEC-03</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>A fresh checkout builds and starts all four applications locally</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Clean clone, .NET 10 SDK, Node 20+ and MySQL 8.4 installed</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>1. Build DealerOps.Core, DealerOps.AiService, DealerOps.Gateway and DealerOps.Logging
+2. Build the React app
+3. Run ./start-local.sh
+4. Poll /actuator/health on 8081, 8082 and 8080, then open the web app</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>All projects build without error, each service reports UP in dependency order, and the web app loads on 5174 and signs in through the gateway only</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>Not executed (planned)</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>Local clean checkout + Azure dev resource group (Terraform, deploy.sh)</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>Yuandong Yang</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>Phase: deployment; smoke bundle entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>DEP-02</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>SEC-04</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>The start-up schema creation and the idempotent column patches are safe to re-run</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>An empty database and a database from an earlier build</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>1. Start core against an empty database and list the created tables
+2. Stop it, add rows, and start it again
+3. Compare the row counts and the patched columns</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>The first start creates the schema, the second adds only missing columns, and no existing row is changed or dropped</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>Not executed (planned)</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>Local clean checkout + Azure dev resource group (Terraform, deploy.sh)</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>Daniel Watson</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>Phase: deployment; EnsureCreated plus start-up patches</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>DEP-03</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>SEC-04</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>The committed demo seed loads and its reset removes only seeded data</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Core started once so the schema exists; MySQL credentials available in the environment</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>1. Run dealer-platform/seed/scripts/load-seed.sh
+2. Count the seeded dealerships, vehicles, customers and listings
+3. Add one record of your own
+4. Re-run with --reset and count again</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>The seed loads every business table with at least 30 rows, the reset removes the 30 seed dealerships and what they own, and the record added by hand survives</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Not executed (planned)</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>Local clean checkout + Azure dev resource group (Terraform, deploy.sh)</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>Daniel Watson</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>Phase: deployment; test-data pipeline check</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>DEP-04</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>SEC-03, SEC-04</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Terraform builds the cloud stack with secrets in Key Vault and HTTPS only</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Azure subscription selected; deploy/terraform configured</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>1. Run terraform apply in deploy/terraform
+2. List the created resources
+3. Open each web app over HTTP and over HTTPS
+4. Grep the repository for a secret value</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>The resource group, App Service plan, four web apps, MySQL flexible server, Key Vault, Log Analytics and Application Insights exist; application settings reference Key Vault; HTTP redirects to HTTPS; no secret is committed</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>Not executed (planned)</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>Local clean checkout + Azure dev resource group (Terraform, deploy.sh)</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>Yuandong Yang</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>Phase: deployment; cloud environment gate for Sprint 2 and 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>DEP-05</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>SEC-03</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>The one-command deployment refuses an unclean tree and publishes a verified build</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>DEP-04 complete; a local change staged on purpose</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>1. Run ./deploy/deploy.sh --apply --seed with an uncommitted change present
+2. Commit and push, then run it again
+3. Read the data export, backup and replace steps in its output
+4. Open /actuator/release through the cloud gateway</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>The first run refuses to publish and names the dirty files; the second uploads all four apps, backs the Azure rows up before replacing them, restarts core, and the release endpoint reports the four apps built from the pushed commit</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Not executed (planned)</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>Local clean checkout + Azure dev resource group (Terraform, deploy.sh)</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>Yuandong Yang</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>Phase: deployment; release procedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>DEP-06</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>SEC-04</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>The data rollback and the stack rebuild both work after a failed release</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>DEP-05 complete; an Azure backup file from that run</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>1. Note the current cloud row counts
+2. Import deploy/seed/azure-backup-&lt;time&gt;.sql.gz
+3. Compare the row counts with the backup
+4. Run terraform destroy and apply once more</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>The import restores exactly the backed-up rows, the cloud demo signs in again afterwards, and destroy followed by apply rebuilds the stack with no manual portal step</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>Not executed (planned)</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>Local clean checkout + Azure dev resource group (Terraform, deploy.sh)</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>Yuandong Yang</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>Phase: deployment; rollback drill</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:N71"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3962,35 +5211,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>DealerOps Group Assignment 2 — Test Cases</t>
+          <t>DealerOps Group Assignment 2 - Test Cases</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Group:</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Group 12 (team G2)</t>
+          <t>Group 12</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Members:</t>
         </is>
@@ -4002,7 +5252,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Course:</t>
         </is>
@@ -4014,118 +5264,198 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Document version:</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>v1.0 (2026-10-13)</t>
+          <t>v2.0 (2026-10-23)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>System under test:</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DealerOps - React 19 web app, YARP gateway, ASP.NET Core 10 core and AI service, MySQL 8.4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Phase</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
+          <t>Companion document:</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>DealerOps_Group_Assignment_2_Test_Plan.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Development phase</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>ID range</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Requirements/design review</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>ST-01 – ST-05</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>UT-01 – UT-10</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>10</v>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>Requirements and design review</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IT-01 – IT-20</t>
+          <t>RV-01 - RV-06</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>20</v>
+        <v>6</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Yuandong Yang (QA lead)</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SYS-01 – SYS-10</t>
+          <t>UT-01 - UT-12</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Daniel Watson and Xiaomei He</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Acceptance</t>
+          <t>Integration / API</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AT-01 – AT-10</t>
+          <t>IT-01 - IT-26</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>26</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Daniel Watson (platform) and Xiaomei He (ads and AI)</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>System (browser end-to-end)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SYS-01 - SYS-12</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>12</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Daniel Watson</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Acceptance</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>AT-01 - AT-08</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>8</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Yuandong Yang with the client representative</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Deployment and release</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>DEP-01 - DEP-06</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>6</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Yuandong Yang</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="n">
-        <v>55</v>
+      <c r="C17" s="4" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Test Status holds the planned value until execution; Actual Result, Test Status and Test Date are filled in during Group Assignment 3.</t>
+        </is>
       </c>
     </row>
   </sheetData>
